--- a/public/exports-60-250/29189420.xlsx
+++ b/public/exports-60-250/29189420.xlsx
@@ -11689,12 +11689,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018578</t>
+          <t xml:space="preserve">310018566</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">310018611</t>
+          <t xml:space="preserve">310018603</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">310020329</t>
+          <t xml:space="preserve">310020316</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -16916,30 +16916,30 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 5</t>
+          <t xml:space="preserve">Halkærvej 42</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">9362</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3290829</t>
+          <t xml:space="preserve">3292310</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J226">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194551</t>
+          <t xml:space="preserve">311207453</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,17 +16949,17 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-15</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halkærvej 42</t>
+          <t xml:space="preserve">Bryggen 9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3292310</t>
+          <t xml:space="preserve">752668, 5558940</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>248</v>
+        <v>76</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207453</t>
+          <t xml:space="preserve">311214352</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Tilstandsrapport-nu.dk ApS</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,35 +17066,35 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 9</t>
+          <t xml:space="preserve">Solhøjsvej 2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">752668, 5558940</t>
+          <t xml:space="preserve">3329160</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J228">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214352</t>
+          <t xml:space="preserve">311214302</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tilstandsrapport-nu.dk ApS</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17141,30 +17141,30 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjsvej 2</t>
+          <t xml:space="preserve">Rosenvænget 1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9370</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3329160</t>
+          <t xml:space="preserve">3265674</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J229">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214302</t>
+          <t xml:space="preserve">311219241</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,17 +17216,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 1</t>
+          <t xml:space="preserve">Bryggen 33</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">9370</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">3265674</t>
+          <t xml:space="preserve">752691, 5558964</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -17235,21 +17235,21 @@
         </is>
       </c>
       <c r="J230">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219241</t>
+          <t xml:space="preserve">311251146</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 33</t>
+          <t xml:space="preserve">Bryggen 40</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">752691, 5558964</t>
+          <t xml:space="preserve">752697, 5558971</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251146</t>
+          <t xml:space="preserve">311327099</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2028-07-19</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 40</t>
+          <t xml:space="preserve">Bryggen 51</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">752697, 5558971</t>
+          <t xml:space="preserve">752709, 5558982</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17389,17 +17389,17 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311327099</t>
+          <t xml:space="preserve">311335875</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-19</t>
+          <t xml:space="preserve">2028-09-12</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 51</t>
+          <t xml:space="preserve">Bryggen 31</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">752709, 5558982</t>
+          <t xml:space="preserve">752689, 5558962</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17464,17 +17464,17 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311335875</t>
+          <t xml:space="preserve">311341145</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Knud Erik Jensen s.m.b.a.</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-12</t>
+          <t xml:space="preserve">2028-10-11</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,40 +17516,40 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 31</t>
+          <t xml:space="preserve">Borgmester Jørgensens Vej 2B</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">752689, 5558962</t>
+          <t xml:space="preserve">5551584</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J234">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311341145</t>
+          <t xml:space="preserve">311462396</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knud Erik Jensen s.m.b.a.</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-11</t>
+          <t xml:space="preserve">2030-09-21</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,40 +17591,40 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Jørgensens Vej 2B</t>
+          <t xml:space="preserve">Søndermarken 29</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9430</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5551584</t>
+          <t xml:space="preserve">8106127</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J235">
-        <v>99</v>
+        <v>196</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311462396</t>
+          <t xml:space="preserve">311465485</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-21</t>
+          <t xml:space="preserve">2030-10-06</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,30 +17666,30 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndermarken 29</t>
+          <t xml:space="preserve">Sogneparken 1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9430</t>
+          <t xml:space="preserve">9370</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">8106127</t>
+          <t xml:space="preserve">8588073</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J236">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465485</t>
+          <t xml:space="preserve">311466943</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-06</t>
+          <t xml:space="preserve">2030-10-13</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sogneparken 1</t>
+          <t xml:space="preserve">Uggerhalnevej 4</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">9370</t>
+          <t xml:space="preserve">9310</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">8588073</t>
+          <t xml:space="preserve">3272545</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311466943</t>
+          <t xml:space="preserve">311471480</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-13</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17831,15 +17831,15 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J238">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471480</t>
+          <t xml:space="preserve">311471472</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uggerhalnevej 4</t>
+          <t xml:space="preserve">Halsvej 199A</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">3272545</t>
+          <t xml:space="preserve">8629998</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J239">
-        <v>146</v>
+        <v>102</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471472</t>
+          <t xml:space="preserve">311472033</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-11-02</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,30 +17966,30 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halsvej 199A</t>
+          <t xml:space="preserve">Gl Skolevej 1A</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">8629998</t>
+          <t xml:space="preserve">8773182</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J240">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311472033</t>
+          <t xml:space="preserve">311474321</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-02</t>
+          <t xml:space="preserve">2030-11-10</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Skolevej 1A</t>
+          <t xml:space="preserve">Gl Skolevej 1B</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18056,15 +18056,15 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J241">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474321</t>
+          <t xml:space="preserve">311474322</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Skolevej 1B</t>
+          <t xml:space="preserve">Gl Skolevej 1C</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,15 +18131,15 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474322</t>
+          <t xml:space="preserve">311474321</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Skolevej 1C</t>
+          <t xml:space="preserve">Bøgemarksvej 11</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8773182</t>
+          <t xml:space="preserve">3307689</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J243">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474321</t>
+          <t xml:space="preserve">311474777</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-10</t>
+          <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgemarksvej 11</t>
+          <t xml:space="preserve">Svenstrup Skolevej 17</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,20 +18276,20 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3307689</t>
+          <t xml:space="preserve">3308322</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J244">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474777</t>
+          <t xml:space="preserve">311474768</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18341,17 +18341,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svenstrup Skolevej 17</t>
+          <t xml:space="preserve">Skansevej 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9400</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3308322</t>
+          <t xml:space="preserve">5560917</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,11 +18360,11 @@
         </is>
       </c>
       <c r="J245">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474768</t>
+          <t xml:space="preserve">311475399</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-11</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 2</t>
+          <t xml:space="preserve">Stolpedalsvej 2</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9400</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5560917</t>
+          <t xml:space="preserve">3300213</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475399</t>
+          <t xml:space="preserve">311479720</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-01</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18506,15 +18506,15 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J247">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479720</t>
+          <t xml:space="preserve">311479722</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18581,15 +18581,15 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J248">
-        <v>194</v>
+        <v>118</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479722</t>
+          <t xml:space="preserve">311479714</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18656,11 +18656,11 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J249">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -18716,40 +18716,40 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpedalsvej 2</t>
+          <t xml:space="preserve">Tofthøjvej 32</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9280</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300213</t>
+          <t xml:space="preserve">10014685</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J250">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479714</t>
+          <t xml:space="preserve">311483926</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-01</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,30 +18791,30 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofthøjvej 32</t>
+          <t xml:space="preserve">Stadionvej 2</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">10014685</t>
+          <t xml:space="preserve">3309849</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J251">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483926</t>
+          <t xml:space="preserve">311484159</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2030-12-19</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18881,15 +18881,15 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J252">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484159</t>
+          <t xml:space="preserve">311484157</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18956,15 +18956,15 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J253">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484157</t>
+          <t xml:space="preserve">311484158</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J254">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484158</t>
+          <t xml:space="preserve">311484159</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19106,15 +19106,15 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J255">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484159</t>
+          <t xml:space="preserve">311484160</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 2</t>
+          <t xml:space="preserve">Bryggen 52A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19176,30 +19176,30 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">3309849</t>
+          <t xml:space="preserve">752724, 5558998</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J256">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484160</t>
+          <t xml:space="preserve">311488365</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-19</t>
+          <t xml:space="preserve">2031-01-14</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 52A</t>
+          <t xml:space="preserve">Nymøllevej 116A</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,30 +19251,30 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">752724, 5558998</t>
+          <t xml:space="preserve">7227793</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J257">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488365</t>
+          <t xml:space="preserve">311501672</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-14</t>
+          <t xml:space="preserve">2031-03-09</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymøllevej 116A</t>
+          <t xml:space="preserve">Frejlev Skolevej 7</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9200</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">7227793</t>
+          <t xml:space="preserve">3302428</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J258">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311501672</t>
+          <t xml:space="preserve">311510924</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-09</t>
+          <t xml:space="preserve">2031-04-08</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,40 +19391,40 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frejlev Skolevej 7</t>
+          <t xml:space="preserve">Stolpedalsvej 2</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">3302428</t>
+          <t xml:space="preserve">3300213</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J259">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510924</t>
+          <t xml:space="preserve">311534087</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-08</t>
+          <t xml:space="preserve">2031-07-06</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19481,11 +19481,11 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J260">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -19541,40 +19541,40 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpedalsvej 2</t>
+          <t xml:space="preserve">Grenen 4</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9260</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300213</t>
+          <t xml:space="preserve">7769465</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J261">
-        <v>116</v>
+        <v>246</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534087</t>
+          <t xml:space="preserve">311547291</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-06</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,30 +19616,30 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grenen 4</t>
+          <t xml:space="preserve">Lange Müllers Vej 18</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9260</t>
+          <t xml:space="preserve">9200</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">7769465</t>
+          <t xml:space="preserve">9820152</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J262">
-        <v>246</v>
+        <v>165</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547291</t>
+          <t xml:space="preserve">311555495</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19706,11 +19706,11 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J263">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -19766,35 +19766,35 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lange Müllers Vej 18</t>
+          <t xml:space="preserve">Rebildparken 63</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200</t>
+          <t xml:space="preserve">9220</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">9820152</t>
+          <t xml:space="preserve">398940</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J264">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555495</t>
+          <t xml:space="preserve">311555618</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rebildparken 63</t>
+          <t xml:space="preserve">Willy Brandts Vej 26</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,30 +19851,30 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">398940</t>
+          <t xml:space="preserve">7467782</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J265">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555618</t>
+          <t xml:space="preserve">311558273</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Willy Brandts Vej 26</t>
+          <t xml:space="preserve">Frøstrupvej 2</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,20 +19926,20 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">7467782</t>
+          <t xml:space="preserve">5553892</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J266">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558273</t>
+          <t xml:space="preserve">311560891</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-11-10</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøstrupvej 2</t>
+          <t xml:space="preserve">Frøstrupvej 4</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20006,15 +20006,15 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J267">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560891</t>
+          <t xml:space="preserve">311560894</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20081,15 +20081,15 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J268">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560894</t>
+          <t xml:space="preserve">311560889</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøstrupvej 4</t>
+          <t xml:space="preserve">Frøstrupvej 6</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20156,15 +20156,15 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J269">
-        <v>132</v>
+        <v>213</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560889</t>
+          <t xml:space="preserve">311560887</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frøstrupvej 6</t>
+          <t xml:space="preserve">Tostrupvej 13C</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5553892</t>
+          <t xml:space="preserve">3304453</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J270">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560887</t>
+          <t xml:space="preserve">311561289</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-10</t>
+          <t xml:space="preserve">2031-11-11</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,30 +20291,30 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tostrupvej 13C</t>
+          <t xml:space="preserve">Frejlev Skolevej 3</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9200</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3304453</t>
+          <t xml:space="preserve">3302429</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J271">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561289</t>
+          <t xml:space="preserve">311567502</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-11</t>
+          <t xml:space="preserve">2031-12-13</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frejlev Skolevej 3</t>
+          <t xml:space="preserve">Godthåbsgade 8</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200</t>
+          <t xml:space="preserve">9400</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3302429</t>
+          <t xml:space="preserve">8289437</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J272">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567502</t>
+          <t xml:space="preserve">311568985</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-13</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20441,30 +20441,30 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsgade 8</t>
+          <t xml:space="preserve">Hørgårdsvej 6</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9400</t>
+          <t xml:space="preserve">9310</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">8289437</t>
+          <t xml:space="preserve">3274606</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J273">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568985</t>
+          <t xml:space="preserve">311569468</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,30 +20516,30 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørgårdsvej 6</t>
+          <t xml:space="preserve">Harald Jensens Vej 3</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">3274606</t>
+          <t xml:space="preserve">8789488</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J274">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569468</t>
+          <t xml:space="preserve">311570329</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Jensens Vej 3</t>
+          <t xml:space="preserve">Harald Jensens Vej 5</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20606,11 +20606,11 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J275">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harald Jensens Vej 5</t>
+          <t xml:space="preserve">Lilletoften 6</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,20 +20676,20 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">8789488</t>
+          <t xml:space="preserve">8930554</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J276">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570329</t>
+          <t xml:space="preserve">311571893</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20756,11 +20756,11 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J277">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -20831,11 +20831,11 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J278">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20891,30 +20891,30 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lilletoften 6</t>
+          <t xml:space="preserve">Vissevej 40D</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9210</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">8930554</t>
+          <t xml:space="preserve">7718916</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J279">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571893</t>
+          <t xml:space="preserve">311573412</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-01-19</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,30 +20966,30 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vissevej 40D</t>
+          <t xml:space="preserve">Kjellerupsgade 20</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">7718916</t>
+          <t xml:space="preserve">7003207</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J280">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311573412</t>
+          <t xml:space="preserve">311577659</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20999,7 +20999,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-19</t>
+          <t xml:space="preserve">2032-02-09</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21041,30 +21041,30 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjellerupsgade 20</t>
+          <t xml:space="preserve">Birkesøvej 13</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9280</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003207</t>
+          <t xml:space="preserve">8518195</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J281">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577659</t>
+          <t xml:space="preserve">311579668</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-09</t>
+          <t xml:space="preserve">2032-02-18</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkesøvej 13</t>
+          <t xml:space="preserve">Birkesøvej 15</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">8518195</t>
+          <t xml:space="preserve">7177031</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -21135,11 +21135,11 @@
         </is>
       </c>
       <c r="J282">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579668</t>
+          <t xml:space="preserve">311579672</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21191,40 +21191,40 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkesøvej 15</t>
+          <t xml:space="preserve">Kayerødsgade 46A</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">7177031</t>
+          <t xml:space="preserve">5541623</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J283">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311579672</t>
+          <t xml:space="preserve">311711599</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-18</t>
+          <t xml:space="preserve">2033-09-30</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,40 +21266,40 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kayerødsgade 46A</t>
+          <t xml:space="preserve">Bryggen 35</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5541623</t>
+          <t xml:space="preserve">752693, 5558966</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>250</v>
+        <v>76</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711599</t>
+          <t xml:space="preserve">311775987</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-30</t>
+          <t xml:space="preserve">2034-08-01</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,40 +21341,40 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 35</t>
+          <t xml:space="preserve">Hålsvej 4</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9260</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">752693, 5558966</t>
+          <t xml:space="preserve">3316478</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J285">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311775987</t>
+          <t xml:space="preserve">311827331</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-01</t>
+          <t xml:space="preserve">2034-12-11</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hålsvej 4</t>
+          <t xml:space="preserve">Nøvling Skolevej 5</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,20 +21426,20 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">3316478</t>
+          <t xml:space="preserve">3324377</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J286">
-        <v>243</v>
+        <v>124</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827331</t>
+          <t xml:space="preserve">311803932</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -21449,7 +21449,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-11</t>
+          <t xml:space="preserve">2034-12-20</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21506,20 +21506,20 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J287">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803932</t>
+          <t xml:space="preserve">311803934</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -21566,17 +21566,17 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøvling Skolevej 5</t>
+          <t xml:space="preserve">Enggårdsgade 65</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">9260</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">3324377</t>
+          <t xml:space="preserve">5546087</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -21585,21 +21585,21 @@
         </is>
       </c>
       <c r="J288">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803934</t>
+          <t xml:space="preserve">311804962</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-20</t>
+          <t xml:space="preserve">2035-01-08</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,30 +21641,30 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggårdsgade 65</t>
+          <t xml:space="preserve">Sofiendalsvej 80</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9200</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5546087</t>
+          <t xml:space="preserve">8974261</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J289">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311804962</t>
+          <t xml:space="preserve">311806110</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-08</t>
+          <t xml:space="preserve">2035-01-15</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21731,15 +21731,15 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J290">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311806110</t>
+          <t xml:space="preserve">311806108</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21806,11 +21806,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J291">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21866,30 +21866,30 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofiendalsvej 80</t>
+          <t xml:space="preserve">Lindholmsvej 136B</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">9200</t>
+          <t xml:space="preserve">9400</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">8974261</t>
+          <t xml:space="preserve">3283667</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J292">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311806108</t>
+          <t xml:space="preserve">311807293</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-15</t>
+          <t xml:space="preserve">2035-01-22</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,30 +21941,30 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindholmsvej 136B</t>
+          <t xml:space="preserve">Gistrup Skolevej 5</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">9400</t>
+          <t xml:space="preserve">9260</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3283667</t>
+          <t xml:space="preserve">3324007</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J293">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807293</t>
+          <t xml:space="preserve">311809152</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-22</t>
+          <t xml:space="preserve">2035-01-31</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,40 +22016,40 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gistrup Skolevej 5</t>
+          <t xml:space="preserve">Bryggen 4</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">9260</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3324007</t>
+          <t xml:space="preserve">752663, 5558935</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J294">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809152</t>
+          <t xml:space="preserve">311815627</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-31</t>
+          <t xml:space="preserve">2035-03-05</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,40 +22091,40 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggen 4</t>
+          <t xml:space="preserve">Padevænget 4</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">752663, 5558935</t>
+          <t xml:space="preserve">5546317, 100797257</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J295">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311815627</t>
+          <t xml:space="preserve">311817850</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">Bygge- og konsulentfirmaet Trynskov ApS</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-05</t>
+          <t xml:space="preserve">2035-03-15</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,40 +22166,40 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padevænget 4</t>
+          <t xml:space="preserve">Nøvling Skolevej 5</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9260</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5546317, 100797257</t>
+          <t xml:space="preserve">3324377</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J296">
-        <v>133</v>
+        <v>230</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311817850</t>
+          <t xml:space="preserve">311826546</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygge- og konsulentfirmaet Trynskov ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-15</t>
+          <t xml:space="preserve">2035-04-23</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,40 +22241,40 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøvling Skolevej 5</t>
+          <t xml:space="preserve">Kong Hans Gade 12</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">9260</t>
+          <t xml:space="preserve">9000</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">3324377</t>
+          <t xml:space="preserve">5542356</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311826546</t>
+          <t xml:space="preserve">311849129</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-23</t>
+          <t xml:space="preserve">2035-08-14</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Gade 12</t>
+          <t xml:space="preserve">Thorsens Alle 25</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5542356</t>
+          <t xml:space="preserve">3298695</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -22335,11 +22335,11 @@
         </is>
       </c>
       <c r="J298">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311849129</t>
+          <t xml:space="preserve">311849133</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22391,30 +22391,30 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorsens Alle 25</t>
+          <t xml:space="preserve">Bautastenen 21</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">9000</t>
+          <t xml:space="preserve">9230</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298695</t>
+          <t xml:space="preserve">3308995</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J299">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311849133</t>
+          <t xml:space="preserve">311849807</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-14</t>
+          <t xml:space="preserve">2035-08-18</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -22466,30 +22466,30 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bautastenen 21</t>
+          <t xml:space="preserve">Aagade 26</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">9230</t>
+          <t xml:space="preserve">9280</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">3308995</t>
+          <t xml:space="preserve">8589375</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>247</v>
+        <v>135</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311849807</t>
+          <t xml:space="preserve">311867758</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-18</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -22541,40 +22541,40 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aagade 26</t>
+          <t xml:space="preserve">Nørholmsvej 480</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280</t>
+          <t xml:space="preserve">9240</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589375</t>
+          <t xml:space="preserve">3305771</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J301">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867758</t>
+          <t xml:space="preserve">311905476</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -22631,11 +22631,11 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J302">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -22691,30 +22691,30 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørholmsvej 480</t>
+          <t xml:space="preserve">Pogevej 5</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">9240</t>
+          <t xml:space="preserve">9382</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">3305771</t>
+          <t xml:space="preserve">3260983</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J303">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905476</t>
+          <t xml:space="preserve">311905601</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22781,15 +22781,15 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J304">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905601</t>
+          <t xml:space="preserve">311907340</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22856,11 +22856,11 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J305">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -22916,30 +22916,30 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pogevej 5</t>
+          <t xml:space="preserve">Aagade 72</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">9382</t>
+          <t xml:space="preserve">9280</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">3260983</t>
+          <t xml:space="preserve">9834657</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J306">
-        <v>119</v>
+        <v>250</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907340</t>
+          <t xml:space="preserve">311909820</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-06-22</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22991,30 +22991,30 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aagade 72</t>
+          <t xml:space="preserve">Bredgade 5</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280</t>
+          <t xml:space="preserve">9362</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">9834657</t>
+          <t xml:space="preserve">3290829</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J307">
-        <v>250</v>
+        <v>127</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909820</t>
+          <t xml:space="preserve">311930278</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-22</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
